--- a/products/Local_Store_GBP_AI_Kit_v0.1.xlsx
+++ b/products/Local_Store_GBP_AI_Kit_v0.1.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="R626c1b9843f941ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Profile" sheetId="2" r:id="Rc98db2be4cd04054"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Post Calendar" sheetId="3" r:id="Rbf79b1b6778d4437"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer Builder" sheetId="4" r:id="R93f999767a024ebd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local FAQ" sheetId="5" r:id="R834220be0fbb455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Reply Builder" sheetId="6" r:id="R353307a842164651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accuracy Check" sheetId="7" r:id="R119b0ebd118546bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Pack" sheetId="8" r:id="R27642ead55574260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="はじめに" sheetId="1" r:id="R730f6017d24d4016"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗情報" sheetId="2" r:id="Rc58bd450d7314d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投稿カレンダー" sheetId="3" r:id="Rb07b9a78085b4042"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企画作成" sheetId="4" r:id="Ra692c1024bef4a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来店前FAQ" sheetId="5" r:id="R3a6582bcb4014074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口コミ返信" sheetId="6" r:id="R6ab4d4369d6d4c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正確性チェック" sheetId="7" r:id="R65424243f3bb41cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロンプト集" sheetId="8" r:id="Rec0405a4576e4fd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,51 +250,58 @@
       </x:c>
       <x:c r="B1" s="7"/>
     </x:row>
-    <x:row r="2" ht="33" customHeight="1"/>
+    <x:row r="2" ht="33" customHeight="1">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+    </x:row>
     <x:row r="3" ht="33" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>飲食店、小売、教室、クリニック以外の地域店舗が、AIでGoogleビジネスプロフィール投稿、FAQ、口コミ返信を作る前に、営業時間、価格、在庫、表現の正確性を確認するためのテンプレートです。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="33" customHeight="1"/>
+      <x:c r="B3"/>
+    </x:row>
+    <x:row r="4" ht="33" customHeight="1">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+    </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
-        <x:v>Step 1</x:v>
+        <x:v>手順 1</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Store Profileに店舗情報、営業時間、強み、注意点を入力</x:v>
+        <x:v>店舗情報に店舗情報、営業時間、強み、注意点を入力</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>Step 2</x:v>
+        <x:v>手順 2</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Post Calendarで週次投稿テーマを作る</x:v>
+        <x:v>投稿 カレンダーで週次投稿テーマを作る</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>Step 3</x:v>
+        <x:v>手順 3</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>Offer Builderで季節メニューやキャンペーンを整理</x:v>
+        <x:v>企画 作成で季節メニューやキャンペーンを整理</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>Step 4</x:v>
+        <x:v>手順 4</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>Local FAQで来店前の不安に答える</x:v>
+        <x:v>来店前FAQで来店前の不安に答える</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
-        <x:v>Step 5</x:v>
+        <x:v>手順 5</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>Accuracy Checkで古い情報、価格、在庫、効果表現を確認</x:v>
+        <x:v>正確性チェックで古い情報、価格、在庫、効果表現を確認</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
@@ -338,359 +345,359 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Field</x:v>
+        <x:v>項目</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Value</x:v>
+        <x:v>入力欄</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Required</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Example</x:v>
+        <x:v>例</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>AI Can Draft?</x:v>
+        <x:v>AIが下書き可?</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Human Must Verify?</x:v>
+        <x:v>人の確認必須?</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Use In</x:v>
+        <x:v>使う範囲</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>店舗名</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str"/>
+      <x:c r="B2" s="6"/>
       <x:c r="C2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
         <x:v>サンプル珈琲</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>All</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="str"/>
+        <x:v>全て</x:v>
+      </x:c>
+      <x:c r="H2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>業種</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="str"/>
+      <x:c r="B3" s="6"/>
       <x:c r="C3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
         <x:v>カフェ / 雑貨 / 教室</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>Post</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="str"/>
+        <x:v>投稿</x:v>
+      </x:c>
+      <x:c r="H3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>住所/エリア</x:v>
       </x:c>
-      <x:c r="B4" s="6" t="str"/>
+      <x:c r="B4" s="6"/>
       <x:c r="C4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
         <x:v>東京都〇〇区</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
-        <x:v>Access</x:v>
-      </x:c>
-      <x:c r="H4" s="6" t="str"/>
+        <x:v>アクセス</x:v>
+      </x:c>
+      <x:c r="H4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>営業時間</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="str"/>
+      <x:c r="B5" s="6"/>
       <x:c r="C5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>10:00-18:00 月曜休み</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>FAQ</x:v>
       </x:c>
-      <x:c r="H5" s="6" t="str"/>
+      <x:c r="H5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>予約/問い合わせ方法</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str"/>
+      <x:c r="B6" s="6"/>
       <x:c r="C6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>電話 / Web / DM</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
-        <x:v>CTA</x:v>
-      </x:c>
-      <x:c r="H6" s="6" t="str"/>
+        <x:v>行動導線</x:v>
+      </x:c>
+      <x:c r="H6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>主な商品/サービス</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="str"/>
+      <x:c r="B7" s="6"/>
       <x:c r="C7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>自家焙煎コーヒー、焼き菓子</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
-        <x:v>Post</x:v>
-      </x:c>
-      <x:c r="H7" s="6" t="str"/>
+        <x:v>投稿</x:v>
+      </x:c>
+      <x:c r="H7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>価格帯</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="str"/>
+      <x:c r="B8" s="6"/>
       <x:c r="C8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
         <x:v>500-1,200円</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
-        <x:v>Offer</x:v>
-      </x:c>
-      <x:c r="H8" s="6" t="str"/>
+        <x:v>企画</x:v>
+      </x:c>
+      <x:c r="H8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>強み</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="str"/>
+      <x:c r="B9" s="6"/>
       <x:c r="C9" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
         <x:v>駅から近い、席が広い</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
-        <x:v>Post</x:v>
-      </x:c>
-      <x:c r="H9" s="6" t="str"/>
+        <x:v>投稿</x:v>
+      </x:c>
+      <x:c r="H9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>来店前の不安</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="str"/>
+      <x:c r="B10" s="6"/>
       <x:c r="C10" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>駐車場、混雑、子連れ可</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
         <x:v>FAQ</x:v>
       </x:c>
-      <x:c r="H10" s="6" t="str"/>
+      <x:c r="H10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>季節情報</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str"/>
+      <x:c r="B11" s="6"/>
       <x:c r="C11" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
         <x:v>春限定メニュー</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
-        <x:v>Offer</x:v>
-      </x:c>
-      <x:c r="H11" s="6" t="str"/>
+        <x:v>企画</x:v>
+      </x:c>
+      <x:c r="H11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>在庫/数量制限</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="str"/>
+      <x:c r="B12" s="6"/>
       <x:c r="C12" s="6" t="str">
-        <x:v>If any</x:v>
+        <x:v>あれば</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>1日20個限定</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
-        <x:v>Offer</x:v>
-      </x:c>
-      <x:c r="H12" s="6" t="str"/>
+        <x:v>企画</x:v>
+      </x:c>
+      <x:c r="H12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>写真で見せたいもの</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="str"/>
+      <x:c r="B13" s="6"/>
       <x:c r="C13" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
         <x:v>外観、席、商品、スタッフ</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
-        <x:v>Photo</x:v>
-      </x:c>
-      <x:c r="H13" s="6" t="str"/>
+        <x:v>写真</x:v>
+      </x:c>
+      <x:c r="H13" s="6"/>
     </x:row>
     <x:row r="14" ht="33" hidden="0" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>避けたい表現</x:v>
       </x:c>
-      <x:c r="B14" s="6" t="str"/>
+      <x:c r="B14" s="6"/>
       <x:c r="C14" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
         <x:v>地域No.1、絶対、治る</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
-        <x:v>Safety</x:v>
-      </x:c>
-      <x:c r="H14" s="6" t="str"/>
+        <x:v>安全</x:v>
+      </x:c>
+      <x:c r="H14" s="6"/>
     </x:row>
     <x:row r="15" ht="33" hidden="0" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>競合との差</x:v>
       </x:c>
-      <x:c r="B15" s="6" t="str"/>
+      <x:c r="B15" s="6"/>
       <x:c r="C15" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
         <x:v>静かな席、豆の種類</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
-        <x:v>Post</x:v>
-      </x:c>
-      <x:c r="H15" s="6" t="str"/>
+        <x:v>投稿</x:v>
+      </x:c>
+      <x:c r="H15" s="6"/>
     </x:row>
     <x:row r="16" ht="33" hidden="0" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>更新頻度</x:v>
       </x:c>
-      <x:c r="B16" s="6" t="str"/>
+      <x:c r="B16" s="6"/>
       <x:c r="C16" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
         <x:v>週2回</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
-        <x:v>Calendar</x:v>
-      </x:c>
-      <x:c r="H16" s="6" t="str"/>
+        <x:v>カレンダー</x:v>
+      </x:c>
+      <x:c r="H16" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -713,28 +720,28 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Post Type</x:v>
+        <x:v>投稿タイプ</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Goal</x:v>
+        <x:v>目的</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Input Needed</x:v>
+        <x:v>必要な入力</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>AI Output</x:v>
+        <x:v>AIの出力</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>CTA</x:v>
+        <x:v>行動導線</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Example Hook</x:v>
+        <x:v>書き出し例</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Metric</x:v>
+        <x:v>指標</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -991,25 +998,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Offer</x:v>
+        <x:v>企画</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Period</x:v>
+        <x:v>期間</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Price</x:v>
+        <x:v>価格</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Limit</x:v>
+        <x:v>制限</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Who It Helps</x:v>
+        <x:v>役立つ相手</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Proof Needed</x:v>
+        <x:v>必要な根拠</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Post Angle</x:v>
+        <x:v>投稿切り口</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1043,7 +1050,7 @@
         <x:v>今月中</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>10% off</x:v>
+        <x:v>10% 割引</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
         <x:v>初回のみ</x:v>
@@ -1215,22 +1222,22 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Question</x:v>
+        <x:v>質問</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Answer Draft</x:v>
+        <x:v>回答案</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Use In</x:v>
+        <x:v>使う範囲</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Avoid</x:v>
+        <x:v>避けること</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1249,7 +1256,7 @@
       <x:c r="E2" s="6" t="str">
         <x:v>必ず入れます</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str"/>
+      <x:c r="F2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1262,12 +1269,12 @@
         <x:v>提携/料金</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Access</x:v>
+        <x:v>アクセス</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
         <x:v>無料ですと断定</x:v>
       </x:c>
-      <x:c r="F3" s="6" t="str"/>
+      <x:c r="F3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1285,7 +1292,7 @@
       <x:c r="E4" s="6" t="str">
         <x:v>必ずOK</x:v>
       </x:c>
-      <x:c r="F4" s="6" t="str"/>
+      <x:c r="F4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1303,7 +1310,7 @@
       <x:c r="E5" s="6" t="str">
         <x:v>未対応を記載</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="str"/>
+      <x:c r="F5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1316,12 +1323,12 @@
         <x:v>実態</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>Post</x:v>
+        <x:v>投稿</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
         <x:v>いつでも空いています</x:v>
       </x:c>
-      <x:c r="F6" s="6" t="str"/>
+      <x:c r="F6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -1339,7 +1346,7 @@
       <x:c r="E7" s="6" t="str">
         <x:v>完全対応</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="str"/>
+      <x:c r="F7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -1357,7 +1364,7 @@
       <x:c r="E8" s="6" t="str">
         <x:v>全部可能</x:v>
       </x:c>
-      <x:c r="F8" s="6" t="str"/>
+      <x:c r="F8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -1375,7 +1382,7 @@
       <x:c r="E9" s="6" t="str">
         <x:v>必ずOK</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="str"/>
+      <x:c r="F9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -1388,12 +1395,12 @@
         <x:v>写真</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>Post</x:v>
+        <x:v>投稿</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
         <x:v>誰でも安心</x:v>
       </x:c>
-      <x:c r="F10" s="6" t="str"/>
+      <x:c r="F10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -1411,7 +1418,7 @@
       <x:c r="E11" s="6" t="str">
         <x:v>必ず即時</x:v>
       </x:c>
-      <x:c r="F11" s="6" t="str"/>
+      <x:c r="F11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6"/>
@@ -1440,22 +1447,22 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Review Type</x:v>
+        <x:v>口コミ種別</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Reply Goal</x:v>
+        <x:v>返信目的</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Reply Structure</x:v>
+        <x:v>返信構成</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Include</x:v>
+        <x:v>入れること</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Avoid</x:v>
+        <x:v>避けること</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Example Phrase</x:v>
+        <x:v>表現例</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1638,25 +1645,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Check</x:v>
+        <x:v>確認項目</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Why</x:v>
+        <x:v>理由</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Risky Example</x:v>
+        <x:v>危ない例</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Safer Direction</x:v>
+        <x:v>安全な方向</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Severity</x:v>
+        <x:v>重要度</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1676,9 +1683,9 @@
         <x:v>営業カレンダー</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1697,9 +1704,9 @@
         <x:v>メニュー表</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1718,9 +1725,9 @@
         <x:v>在庫</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1739,9 +1746,9 @@
         <x:v>表現</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1760,9 +1767,9 @@
         <x:v>表現</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -1781,9 +1788,9 @@
         <x:v>根拠</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="str"/>
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="G7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -1802,9 +1809,9 @@
         <x:v>許可</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -1823,9 +1830,9 @@
         <x:v>条件</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="str"/>
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="G9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -1844,9 +1851,9 @@
         <x:v>地図</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="str"/>
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="G10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -1865,9 +1872,9 @@
         <x:v>個人情報</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -1886,9 +1893,9 @@
         <x:v>実態</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="str"/>
+        <x:v>低</x:v>
+      </x:c>
+      <x:c r="G12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -1907,9 +1914,9 @@
         <x:v>導線</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="str"/>
+        <x:v>低</x:v>
+      </x:c>
+      <x:c r="G13" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1928,16 +1935,16 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Prompt</x:v>
+        <x:v>プロンプト</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Use</x:v>
+        <x:v>用途</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Text</x:v>
+        <x:v>本文</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
